--- a/笔记.xlsx
+++ b/笔记.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\yuri_pyfulent_tkinter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63318F84-00C9-489E-8E7D-311B72DD2071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4F4E4B-C384-42EA-BFEB-854CBD7F81DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="2535" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
